--- a/Models/Птицы/results/Птица - Результаты прогнозов ХВ.xlsx
+++ b/Models/Птицы/results/Птица - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[8370.33, 8231.05, 8993.66]</t>
+          <t>[11268.8, 10962.08, 10960.74]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[8963.23, 9586.12, 10969.85]</t>
+          <t>[10080.07, 10273.59, 10251.41]</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1425.136121587208</v>
+        <v>892.6094827702216</v>
       </c>
       <c r="G2" t="n">
-        <v>1308.049380914826</v>
+        <v>862.1846378463251</v>
       </c>
       <c r="H2" t="n">
-        <v>12.9217245206005</v>
+        <v>8.471268755653366</v>
       </c>
     </row>
     <row r="3">
@@ -514,32 +514,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[8580.64, 9371.93, 9503.97]</t>
+          <t>[10252.48, 10257.31, 10525.67]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[9586.12, 10969.85, 10894.97]</t>
+          <t>[10273.59, 10251.41, 8665.21]</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1353.910516061802</v>
+        <v>1074.212534381919</v>
       </c>
       <c r="G3" t="n">
-        <v>1331.467288233481</v>
+        <v>629.156355162048</v>
       </c>
       <c r="H3" t="n">
-        <v>12.60758907493835</v>
+        <v>7.244493332372278</v>
       </c>
     </row>
     <row r="4">
@@ -550,32 +550,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[10018.67, 10153.83, 9794.54]</t>
+          <t>[10269.94, 10538.61, 11740.42]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>[10969.85, 10894.97, 10238.97]</t>
+          <t>[10251.41, 8665.21, 11438.74]</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>741.9672475378203</v>
+        <v>1095.594893126972</v>
       </c>
       <c r="G4" t="n">
-        <v>712.24898906484</v>
+        <v>731.2018911340662</v>
       </c>
       <c r="H4" t="n">
-        <v>6.604663501832619</v>
+        <v>8.145952126041706</v>
       </c>
     </row>
     <row r="5">
@@ -586,32 +586,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[10726.45, 10344.52, 10434.36]</t>
+          <t>[10527.16, 11727.89, 9571.69]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[10894.97, 10238.97, 12692.46]</t>
+          <t>[8665.21, 11438.74, 8560.3]</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1308.761596846275</v>
+        <v>1234.690020658441</v>
       </c>
       <c r="G5" t="n">
-        <v>844.0579865743324</v>
+        <v>1054.16384293969</v>
       </c>
       <c r="H5" t="n">
-        <v>6.789514371498161</v>
+        <v>11.94345607360405</v>
       </c>
     </row>
     <row r="6">
@@ -622,32 +622,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[10440.63, 10530.26, 10506.03]</t>
+          <t>[10434.02, 8525.1, 8451.39]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[10238.97, 12692.46, 10379.17]</t>
+          <t>[11438.74, 8560.3, 12551.51]</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1255.900676685879</v>
+        <v>2437.326794725338</v>
       </c>
       <c r="G6" t="n">
-        <v>830.2396854054823</v>
+        <v>1713.346777787133</v>
       </c>
       <c r="H6" t="n">
-        <v>6.742365111830613</v>
+        <v>13.95367956970975</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +658,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[10406.79, 10383.98, 10758.81]</t>
+          <t>[9008.93, 8927.08, 9793.45]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[12692.46, 10379.17, 10080.07]</t>
+          <t>[8560.3, 12551.51, 12385.3]</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1376.590101839953</v>
+        <v>2585.565704961902</v>
       </c>
       <c r="G7" t="n">
-        <v>989.7381911587696</v>
+        <v>2221.635714095212</v>
       </c>
       <c r="H7" t="n">
-        <v>8.262622134970488</v>
+        <v>18.34801947173558</v>
       </c>
     </row>
     <row r="8">
@@ -694,32 +694,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[11709.27, 12119.13, 11782.03]</t>
+          <t>[8657.41, 9499.93, 9613.75]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[10379.17, 10080.07, 10273.59]</t>
+          <t>[12551.51, 12385.3, 13015.9]</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1653.515250657747</v>
+        <v>3418.772259193778</v>
       </c>
       <c r="G8" t="n">
-        <v>1625.868603645246</v>
+        <v>3393.873922258499</v>
       </c>
       <c r="H8" t="n">
-        <v>15.90882391450214</v>
+        <v>26.82003793140175</v>
       </c>
     </row>
     <row r="9">
@@ -730,32 +730,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[11268.8, 10962.08, 10960.74]</t>
+          <t>[11848.66, 11967.59, 11500.33]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>[10080.07, 10273.59, 10251.41]</t>
+          <t>[12385.3, 13015.9, 10609.0]</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>892.6094827702216</v>
+        <v>852.7209433955005</v>
       </c>
       <c r="G9" t="n">
-        <v>862.1846378463251</v>
+        <v>825.4256895389899</v>
       </c>
       <c r="H9" t="n">
-        <v>8.471268755653366</v>
+        <v>6.929523572519337</v>
       </c>
     </row>
     <row r="10">
@@ -766,32 +766,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[10252.48, 10257.31, 10525.67]</t>
+          <t>[12295.23, 11811.83, 12149.46]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>[10273.59, 10251.41, 8665.21]</t>
+          <t>[13015.9, 10609.0, 10408.6]</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1074.212534381919</v>
+        <v>1290.578534029727</v>
       </c>
       <c r="G10" t="n">
-        <v>629.156355162048</v>
+        <v>1221.454788752206</v>
       </c>
       <c r="H10" t="n">
-        <v>7.244493332372278</v>
+        <v>11.19997601100219</v>
       </c>
     </row>
     <row r="11">
@@ -802,32 +802,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[10269.94, 10538.61, 11740.42]</t>
+          <t>[12224.16, 12570.27, 12279.38]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[10251.41, 8665.21, 11438.74]</t>
+          <t>[10609.0, 10408.6, 10639.7]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1095.594893126972</v>
+        <v>1823.010890530646</v>
       </c>
       <c r="G11" t="n">
-        <v>731.2018911340662</v>
+        <v>1805.503266836275</v>
       </c>
       <c r="H11" t="n">
-        <v>8.145952126041706</v>
+        <v>17.13450178544102</v>
       </c>
     </row>
     <row r="12">
@@ -838,32 +838,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[61.67, 45.75, 19.9]</t>
+          <t>[63.12, 59.37, 95.38]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[64.3, 56.5, 82.4]</t>
+          <t>[68.4, 1.6, 65.0]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>36.64288621333411</v>
+        <v>37.80826056822875</v>
       </c>
       <c r="G12" t="n">
-        <v>25.29064224264033</v>
+        <v>31.14489407484342</v>
       </c>
       <c r="H12" t="n">
-        <v>32.98489061116605</v>
+        <v>1221.757031239664</v>
       </c>
     </row>
     <row r="13">
@@ -874,32 +874,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[46.13, 20.07, 45.75]</t>
+          <t>[60.38, 96.96, 130.58]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[56.5, 82.4, 53.6]</t>
+          <t>[1.6, 65.0, 61.3]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>36.7602162405196</v>
+        <v>55.60654902378923</v>
       </c>
       <c r="G13" t="n">
-        <v>26.84964858113789</v>
+        <v>53.34003086084368</v>
       </c>
       <c r="H13" t="n">
-        <v>36.2140876074198</v>
+        <v>1278.61343553156</v>
       </c>
     </row>
     <row r="14">
@@ -910,32 +910,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[20.91, 47.59, 53.5]</t>
+          <t>[53.99, 73.25, 159.68]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[82.4, 53.6, 37.0]</t>
+          <t>[65.0, 61.3, 254.2]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>36.9189830415479</v>
+        <v>55.37387389018878</v>
       </c>
       <c r="G14" t="n">
-        <v>27.99816348063281</v>
+        <v>39.16081854077365</v>
       </c>
       <c r="H14" t="n">
-        <v>43.4734348068129</v>
+        <v>24.53830803795371</v>
       </c>
     </row>
     <row r="15">
@@ -946,32 +946,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[62.45, 69.99, 28.91]</t>
+          <t>[75.87, 165.32, 55.58]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[53.6, 37.0, 46.4]</t>
+          <t>[61.3, 254.2, 54.3]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>22.1544122511311</v>
+        <v>52.00564237224189</v>
       </c>
       <c r="G15" t="n">
-        <v>19.77674733643712</v>
+        <v>34.9113071015808</v>
       </c>
       <c r="H15" t="n">
-        <v>47.78859493486869</v>
+        <v>20.36534479250525</v>
       </c>
     </row>
     <row r="16">
@@ -982,32 +982,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[67.77, 27.98, 24.21]</t>
+          <t>[159.0, 53.46, 40.35]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[37.0, 46.4, 52.6]</t>
+          <t>[254.2, 54.3, 30.5]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>26.40777396363673</v>
+        <v>55.25720349644827</v>
       </c>
       <c r="G16" t="n">
-        <v>25.8603599337123</v>
+        <v>35.29572657645775</v>
       </c>
       <c r="H16" t="n">
-        <v>58.94583975266885</v>
+        <v>23.76582233936114</v>
       </c>
     </row>
     <row r="17">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[24.75, 21.43, 47.99]</t>
+          <t>[58.2, 43.92, 21.6]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[46.4, 52.6, 68.4]</t>
+          <t>[54.3, 30.5, 18.0]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>24.88030744777859</v>
+        <v>8.333124622349514</v>
       </c>
       <c r="G17" t="n">
-        <v>24.41137861634889</v>
+        <v>6.974862102847318</v>
       </c>
       <c r="H17" t="n">
-        <v>45.25462316878861</v>
+        <v>23.73442560309293</v>
       </c>
     </row>
     <row r="18">
@@ -1054,32 +1054,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[24.25, 54.09, 50.95]</t>
+          <t>[43.38, 21.34, 42.89]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[52.6, 68.4, 1.6]</t>
+          <t>[30.5, 18.0, 48.6]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>33.88090679724692</v>
+        <v>8.359431179340293</v>
       </c>
       <c r="G18" t="n">
-        <v>30.66968595308834</v>
+        <v>7.309480347371845</v>
       </c>
       <c r="H18" t="n">
-        <v>1053.007866039472</v>
+        <v>24.17143056153432</v>
       </c>
     </row>
     <row r="19">
@@ -1090,32 +1090,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[63.12, 59.37, 95.38]</t>
+          <t>[20.03, 40.34, 43.27]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[68.4, 1.6, 65.0]</t>
+          <t>[18.0, 48.6, 23.9]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>37.80826056822875</v>
+        <v>12.21495100403101</v>
       </c>
       <c r="G19" t="n">
-        <v>31.14489407484342</v>
+        <v>9.887179994153898</v>
       </c>
       <c r="H19" t="n">
-        <v>1221.757031239664</v>
+        <v>36.44523613909878</v>
       </c>
     </row>
     <row r="20">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[60.38, 96.96, 130.58]</t>
+          <t>[39.61, 42.49, 19.5]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[1.6, 65.0, 61.3]</t>
+          <t>[48.6, 23.9, 52.4]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>55.60654902378923</v>
+        <v>22.42562077679481</v>
       </c>
       <c r="G20" t="n">
-        <v>53.34003086084368</v>
+        <v>20.16049766195653</v>
       </c>
       <c r="H20" t="n">
-        <v>1278.61343553156</v>
+        <v>53.02423932307283</v>
       </c>
     </row>
     <row r="21">
@@ -1162,32 +1162,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[53.99, 73.25, 159.68]</t>
+          <t>[44.05, 20.23, 18.02]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[65.0, 61.3, 254.2]</t>
+          <t>[23.9, 52.4, 60.6]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>55.37387389018878</v>
+        <v>32.93158312635715</v>
       </c>
       <c r="G21" t="n">
-        <v>39.16081854077365</v>
+        <v>31.63071545833619</v>
       </c>
       <c r="H21" t="n">
-        <v>24.53830803795371</v>
+        <v>71.9819913073156</v>
       </c>
     </row>
     <row r="22">
@@ -1198,32 +1198,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[11454.42, 10359.82, 11450.11]</t>
+          <t>[10624.04, 10697.37, 11013.89]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[11949.02, 10187.92, 12341.77]</t>
+          <t>[11018.07, 10774.72, 11765.56]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>597.0010286355614</v>
+        <v>492.0180085529105</v>
       </c>
       <c r="G22" t="n">
-        <v>519.3861571514735</v>
+        <v>407.6828231049221</v>
       </c>
       <c r="H22" t="n">
-        <v>4.350422738281435</v>
+        <v>3.560939860710117</v>
       </c>
     </row>
     <row r="23">
@@ -1234,32 +1234,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[10598.09, 11710.71, 11354.71]</t>
+          <t>[10906.92, 11227.69, 10607.28]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[10187.92, 12341.77, 11359.95]</t>
+          <t>[10774.72, 11765.56, 12546.48]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>434.5522177035519</v>
+        <v>1164.368429696173</v>
       </c>
       <c r="G23" t="n">
-        <v>348.8234782363961</v>
+        <v>869.7538158989391</v>
       </c>
       <c r="H23" t="n">
-        <v>3.061792353562327</v>
+        <v>7.084854833328082</v>
       </c>
     </row>
     <row r="24">
@@ -1270,32 +1270,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[11466.81, 11120.33, 10832.47]</t>
+          <t>[11155.48, 10539.56, 13017.56]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[12341.77, 11359.95, 11464.21]</t>
+          <t>[11765.56, 12546.48, 12207.96]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>638.2455411967071</v>
+        <v>1298.123357305133</v>
       </c>
       <c r="G24" t="n">
-        <v>582.1082615526187</v>
+        <v>1142.199933748677</v>
       </c>
       <c r="H24" t="n">
-        <v>4.903114630074209</v>
+        <v>9.270974102262645</v>
       </c>
     </row>
     <row r="25">
@@ -1306,32 +1306,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[11564.96, 11259.65, 11898.02]</t>
+          <t>[10839.03, 13386.28, 13127.52]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[11359.95, 11464.21, 11091.93]</t>
+          <t>[12546.48, 12207.96, 12023.33]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>494.5228582858945</v>
+        <v>1356.840140670415</v>
       </c>
       <c r="G25" t="n">
-        <v>405.220278701209</v>
+        <v>1329.984735600108</v>
       </c>
       <c r="H25" t="n">
-        <v>3.618790846151226</v>
+        <v>10.8149134473132</v>
       </c>
     </row>
     <row r="26">
@@ -1342,32 +1342,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[11154.79, 11787.42, 10603.88]</t>
+          <t>[14475.28, 14186.35, 12732.37]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[11464.21, 11091.93, 12311.95]</t>
+          <t>[12207.96, 12023.33, 10821.1]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1079.653970217424</v>
+        <v>2119.146073797363</v>
       </c>
       <c r="G26" t="n">
-        <v>904.3281374351282</v>
+        <v>2113.869448875515</v>
       </c>
       <c r="H26" t="n">
-        <v>7.61418374158583</v>
+        <v>18.07502952577411</v>
       </c>
     </row>
     <row r="27">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[11960.28, 10758.15, 10083.06]</t>
+          <t>[12972.65, 11653.2, 12984.26]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[11091.93, 12311.95, 11018.07]</t>
+          <t>[12023.33, 10821.1, 12752.96]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1160.828819017803</v>
+        <v>740.968826165612</v>
       </c>
       <c r="G27" t="n">
-        <v>1119.054130993158</v>
+        <v>670.9086772642531</v>
       </c>
       <c r="H27" t="n">
-        <v>9.645032764678746</v>
+        <v>5.799666098323395</v>
       </c>
     </row>
     <row r="28">
@@ -1414,32 +1414,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[10334.06, 9690.69, 9765.44]</t>
+          <t>[11197.5, 12481.83, 12034.29]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[12311.95, 11018.07, 10774.72]</t>
+          <t>[10821.1, 12752.96, 13346.82]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1493.610863393121</v>
+        <v>803.7232354714191</v>
       </c>
       <c r="G28" t="n">
-        <v>1438.182079453308</v>
+        <v>653.3529768318373</v>
       </c>
       <c r="H28" t="n">
-        <v>12.4930594891866</v>
+        <v>5.146143101796572</v>
       </c>
     </row>
     <row r="29">
@@ -1450,32 +1450,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[10624.04, 10697.37, 11013.89]</t>
+          <t>[12259.94, 11821.95, 11550.38]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[11018.07, 10774.72, 11765.56]</t>
+          <t>[12752.96, 13346.82, 11619.21]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>492.0180085529105</v>
+        <v>926.1123329110704</v>
       </c>
       <c r="G29" t="n">
-        <v>407.6828231049221</v>
+        <v>695.5765934453029</v>
       </c>
       <c r="H29" t="n">
-        <v>3.560939860710117</v>
+        <v>5.294450687083003</v>
       </c>
     </row>
     <row r="30">
@@ -1486,32 +1486,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[10906.92, 11227.69, 10607.28]</t>
+          <t>[12067.5, 11788.42, 12344.24]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[10774.72, 11765.56, 12546.48]</t>
+          <t>[13346.82, 11619.21, 10505.14]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1164.368429696173</v>
+        <v>1297.122079411392</v>
       </c>
       <c r="G30" t="n">
-        <v>869.7538158989391</v>
+        <v>1095.87581975083</v>
       </c>
       <c r="H30" t="n">
-        <v>7.084854833328082</v>
+        <v>9.51604640692144</v>
       </c>
     </row>
     <row r="31">
@@ -1522,32 +1522,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[11155.48, 10539.56, 13017.56]</t>
+          <t>[12421.12, 13004.16, 11931.78]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[11765.56, 12546.48, 12207.96]</t>
+          <t>[11619.21, 10505.14, 10844.25]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1298.123357305133</v>
+        <v>1640.211508136109</v>
       </c>
       <c r="G31" t="n">
-        <v>1142.199933748677</v>
+        <v>1462.821689030715</v>
       </c>
       <c r="H31" t="n">
-        <v>9.270974102262645</v>
+        <v>13.57293651792187</v>
       </c>
     </row>
     <row r="32">
@@ -1558,17 +1558,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[-0.52, -0.4, -0.29]</t>
+          <t>[-0.18, -0.31, -0.2]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.4139391366838261</v>
+        <v>0.2354511420868577</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4025358741361861</v>
+        <v>0.2284960143503205</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1596,17 +1596,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[-0.17, -0.01, -0.17]</t>
+          <t>[-0.25, -0.13, 0.46]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.1385585034672868</v>
+        <v>0.3111893588095834</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1161467514464534</v>
+        <v>0.2784211687874935</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1634,29 +1634,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[0.07, -0.1, 1.23]</t>
+          <t>[-0.01, 0.65, 1.54]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.6]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.7151959970336157</v>
+        <v>0.6594980145176373</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4697314243768942</v>
+        <v>0.5341002155471797</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1672,29 +1672,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[-0.13, 1.17, 0.52]</t>
+          <t>[0.66, 1.55, -0.15]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.6, 0.0]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.740867755935958</v>
+        <v>0.6742298019530687</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6057795368805571</v>
+        <v>0.5869674041124613</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1710,29 +1710,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[1.3, 0.62, -0.23]</t>
+          <t>[1.04, -0.32, -0.17]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.6, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.8426594846270939</v>
+        <v>0.328084648028146</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7175070817383133</v>
+        <v>0.3078736887698494</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1748,17 +1748,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[0.12, -0.47, -0.36]</t>
+          <t>[-0.39, -0.25, -0.12]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.3469505582355458</v>
+        <v>0.2740537331259743</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3157201153359584</v>
+        <v>0.2519429723980624</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[-0.49, -0.39, -0.48]</t>
+          <t>[-0.07, 0.09, -0.08]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.4581350103130479</v>
+        <v>0.0778402067391695</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4557510836360066</v>
+        <v>0.07754615793530607</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1824,17 +1824,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[-0.18, -0.31, -0.2]</t>
+          <t>[0.12, -0.05, 1.17]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.2354511420868577</v>
+        <v>0.6769724336504253</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2284960143503205</v>
+        <v>0.4445484338706207</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1862,17 +1862,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[-0.25, -0.13, 0.46]</t>
+          <t>[-0.09, 1.06, 0.5]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.3111893588095834</v>
+        <v>0.6787709677126287</v>
       </c>
       <c r="G40" t="n">
-        <v>0.2784211687874935</v>
+        <v>0.550986373920061</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1900,29 +1900,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[-0.01, 0.65, 1.54]</t>
+          <t>[1.15, 0.56, -0.2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.6]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.6594980145176373</v>
+        <v>0.7490363031471921</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5341002155471797</v>
+        <v>0.6388003953999926</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1938,32 +1938,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[5375.97, 5033.15, 5359.51]</t>
+          <t>[6127.6, 6347.08, 6818.83]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[6353.35, 5898.97, 6673.73]</t>
+          <t>[6144.41, 5613.89, 6157.31]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1069.593795708649</v>
+        <v>570.2230044191738</v>
       </c>
       <c r="G42" t="n">
-        <v>1052.474091237579</v>
+        <v>470.5064346890952</v>
       </c>
       <c r="H42" t="n">
-        <v>16.58455017760518</v>
+        <v>8.025837899881139</v>
       </c>
     </row>
     <row r="43">
@@ -1974,32 +1974,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[5618.75, 5976.07, 5977.26]</t>
+          <t>[6358.53, 6831.02, 7279.08]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[5898.97, 6673.73, 6217.87]</t>
+          <t>[5613.89, 6157.31, 6043.79]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>455.7578089945103</v>
+        <v>919.1155367088481</v>
       </c>
       <c r="G43" t="n">
-        <v>406.1624784735947</v>
+        <v>884.546808851941</v>
       </c>
       <c r="H43" t="n">
-        <v>6.35791837908853</v>
+        <v>14.88162446045631</v>
       </c>
     </row>
     <row r="44">
@@ -2010,32 +2010,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[6172.38, 6170.7, 6299.0]</t>
+          <t>[6293.21, 6710.71, 7025.94]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[6673.73, 6217.87, 6956.45]</t>
+          <t>[6157.31, 6043.79, 5998.19]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>478.1273890090409</v>
+        <v>711.694929904339</v>
       </c>
       <c r="G44" t="n">
-        <v>401.9893285300402</v>
+        <v>610.1898403825317</v>
       </c>
       <c r="H44" t="n">
-        <v>5.907272866691035</v>
+        <v>10.1254200001544</v>
       </c>
     </row>
     <row r="45">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[6502.29, 6633.84, 5884.31]</t>
+          <t>[6613.47, 6924.85, 6050.82]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[6217.87, 6956.45, 6264.3]</t>
+          <t>[6043.79, 5998.19, 6376.96]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>331.3439902046195</v>
+        <v>655.6419985206227</v>
       </c>
       <c r="G45" t="n">
-        <v>329.0076505709379</v>
+        <v>607.4931946543617</v>
       </c>
       <c r="H45" t="n">
-        <v>5.092602108550556</v>
+        <v>9.996402281216799</v>
       </c>
     </row>
     <row r="46">
@@ -2082,32 +2082,32 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[6439.68, 5713.59, 5651.83]</t>
+          <t>[6518.17, 5699.12, 5328.78]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[6956.45, 6264.3, 5826.35]</t>
+          <t>[5998.19, 6376.96, 5574.81]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>447.5079812032845</v>
+        <v>513.2822982715428</v>
       </c>
       <c r="G46" t="n">
-        <v>414.0000333129801</v>
+        <v>481.2841359142309</v>
       </c>
       <c r="H46" t="n">
-        <v>6.405085999292615</v>
+        <v>7.90391926418038</v>
       </c>
     </row>
     <row r="47">
@@ -2118,32 +2118,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[6011.18, 5943.58, 6152.45]</t>
+          <t>[5383.58, 5036.01, 5395.03]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[6264.3, 5826.35, 6144.41]</t>
+          <t>[6376.96, 5574.81, 6469.33]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>161.1203642845106</v>
+        <v>900.2269586645571</v>
       </c>
       <c r="G47" t="n">
-        <v>126.1309523216702</v>
+        <v>868.8253063557064</v>
       </c>
       <c r="H47" t="n">
-        <v>2.061212772451802</v>
+        <v>13.94950618944651</v>
       </c>
     </row>
     <row r="48">
@@ -2154,32 +2154,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[6108.49, 6321.84, 6546.29]</t>
+          <t>[5637.0, 6033.06, 5990.77]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[5826.35, 6144.41, 5613.89]</t>
+          <t>[5574.81, 6469.33, 6486.09]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>571.6788378338257</v>
+        <v>382.7719124029741</v>
       </c>
       <c r="G48" t="n">
-        <v>463.9897240201772</v>
+        <v>331.2605794117608</v>
       </c>
       <c r="H48" t="n">
-        <v>8.112979156323739</v>
+        <v>5.165298263329121</v>
       </c>
     </row>
     <row r="49">
@@ -2190,32 +2190,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[6127.6, 6347.08, 6818.83]</t>
+          <t>[5988.79, 5946.96, 6128.02]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[6144.41, 5613.89, 6157.31]</t>
+          <t>[6469.33, 6486.09, 6221.83]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>570.2230044191738</v>
+        <v>420.4667952765445</v>
       </c>
       <c r="G49" t="n">
-        <v>470.5064346890952</v>
+        <v>371.1586147308705</v>
       </c>
       <c r="H49" t="n">
-        <v>8.025837899881139</v>
+        <v>5.749252636508738</v>
       </c>
     </row>
     <row r="50">
@@ -2226,32 +2226,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[6358.53, 6831.02, 7279.08]</t>
+          <t>[6257.99, 6445.66, 5727.77]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[5613.89, 6157.31, 6043.79]</t>
+          <t>[6486.09, 6221.83, 6069.31]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>919.1155367088481</v>
+        <v>270.0472569241346</v>
       </c>
       <c r="G50" t="n">
-        <v>884.546808851941</v>
+        <v>264.4881232229121</v>
       </c>
       <c r="H50" t="n">
-        <v>14.88162446045631</v>
+        <v>4.247164131310227</v>
       </c>
     </row>
     <row r="51">
@@ -2262,32 +2262,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[6293.21, 6710.71, 7025.94]</t>
+          <t>[6601.32, 5865.18, 5765.27]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[6157.31, 6043.79, 5998.19]</t>
+          <t>[6221.83, 6069.31, 6186.68]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>711.694929904339</v>
+        <v>347.9792416503192</v>
       </c>
       <c r="G51" t="n">
-        <v>610.1898403825317</v>
+        <v>335.0100043283061</v>
       </c>
       <c r="H51" t="n">
-        <v>10.1254200001544</v>
+        <v>5.424738319118311</v>
       </c>
     </row>
     <row r="52">
@@ -2298,32 +2298,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>[0.07, -0.08, -0.05]</t>
+          <t>[0.17, 0.11, 0.17]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>[0.2, 0.1, 0.1]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.1561195312183004</v>
+        <v>0.05795927252395523</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1550291533474311</v>
+        <v>0.05077402017180755</v>
       </c>
       <c r="H52" t="n">
-        <v>132.7116420323649</v>
+        <v>50.77402017180756</v>
       </c>
     </row>
     <row r="53">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>[-0.01, 0.02, 0.02]</t>
+          <t>[0.07, 0.12, 0.22]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.08906624650388516</v>
+        <v>0.07052699098307011</v>
       </c>
       <c r="G53" t="n">
-        <v>0.08799609826111121</v>
+        <v>0.05639669352756549</v>
       </c>
       <c r="H53" t="n">
-        <v>87.99609826111121</v>
+        <v>56.39669352756547</v>
       </c>
     </row>
     <row r="54">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>[0.09, 0.09, 0.06]</t>
+          <t>[0.14, 0.24, 0.08]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2389,13 +2389,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.02699679300626833</v>
+        <v>0.08532656492335326</v>
       </c>
       <c r="G54" t="n">
-        <v>0.02130818484204383</v>
+        <v>0.06878773235558885</v>
       </c>
       <c r="H54" t="n">
-        <v>21.30818484204383</v>
+        <v>68.78773235558884</v>
       </c>
     </row>
     <row r="55">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>[0.1, 0.06, 0.11]</t>
+          <t>[0.21, 0.05, 0.18]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.02333731845687141</v>
+        <v>0.08306458595275304</v>
       </c>
       <c r="G55" t="n">
-        <v>0.01762994294705284</v>
+        <v>0.07926582977765177</v>
       </c>
       <c r="H55" t="n">
-        <v>17.62994294705284</v>
+        <v>79.26582977765176</v>
       </c>
     </row>
     <row r="56">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[0.06, 0.11, 0.1]</t>
+          <t>[-0.01, 0.11, -0.04]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2461,13 +2461,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.02316543816345428</v>
+        <v>0.1018743865318211</v>
       </c>
       <c r="G56" t="n">
-        <v>0.01867764800635756</v>
+        <v>0.08559361887043904</v>
       </c>
       <c r="H56" t="n">
-        <v>18.67764800635756</v>
+        <v>85.59361887043903</v>
       </c>
     </row>
     <row r="57">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[0.14, 0.13, 0.2]</t>
+          <t>[0.19, 0.03, 0.06]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2497,13 +2497,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.0656602790283837</v>
+        <v>0.06897455864546244</v>
       </c>
       <c r="G57" t="n">
-        <v>0.05686287949284211</v>
+        <v>0.06671007591657035</v>
       </c>
       <c r="H57" t="n">
-        <v>56.86287949284211</v>
+        <v>66.71007591657036</v>
       </c>
     </row>
     <row r="58">
@@ -2514,17 +2514,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[0.1, 0.18, 0.11]</t>
+          <t>[-0.02, 0.01, 0.01]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.04515682714421244</v>
+        <v>0.1011148611737556</v>
       </c>
       <c r="G58" t="n">
-        <v>0.03164678138452832</v>
+        <v>0.1003514917477508</v>
       </c>
       <c r="H58" t="n">
-        <v>31.64678138452832</v>
+        <v>100.3514917477508</v>
       </c>
     </row>
     <row r="59">
@@ -2550,17 +2550,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[0.17, 0.11, 0.17]</t>
+          <t>[0.08, 0.08, 0.05]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.05795927252395523</v>
+        <v>0.03175361295964896</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05077402017180755</v>
+        <v>0.02809009890356727</v>
       </c>
       <c r="H59" t="n">
-        <v>50.77402017180756</v>
+        <v>28.09009890356727</v>
       </c>
     </row>
     <row r="60">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[0.07, 0.12, 0.22]</t>
+          <t>[0.1, 0.06, 0.11]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.07052699098307011</v>
+        <v>0.02244346924005693</v>
       </c>
       <c r="G60" t="n">
-        <v>0.05639669352756549</v>
+        <v>0.0169778592498719</v>
       </c>
       <c r="H60" t="n">
-        <v>56.39669352756547</v>
+        <v>16.9778592498719</v>
       </c>
     </row>
     <row r="61">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[0.14, 0.24, 0.08]</t>
+          <t>[0.07, 0.11, 0.1]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.08532656492335326</v>
+        <v>0.02123900337707786</v>
       </c>
       <c r="G61" t="n">
-        <v>0.06878773235558885</v>
+        <v>0.01638580052288138</v>
       </c>
       <c r="H61" t="n">
-        <v>68.78773235558884</v>
+        <v>16.38580052288138</v>
       </c>
     </row>
     <row r="62">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[-0.04, -0.01, -0.05]</t>
+          <t>[0.08, 0.06, 0.11]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.03445069872235706</v>
+        <v>0.08372401296444049</v>
       </c>
       <c r="G62" t="n">
-        <v>0.02992888798574335</v>
+        <v>0.08193386602224169</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0.03, -0.01, 0.01]</t>
+          <t>[-0.01, 0.03, 0.01]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.01974678608633504</v>
+        <v>0.01779470984843827</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01684333941233795</v>
+        <v>0.01552241482970592</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2734,29 +2734,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[-0.04, -0.02, -0.02]</t>
+          <t>[0.04, 0.02, -0.05]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.07399258757836914</v>
+        <v>0.03854038096053812</v>
       </c>
       <c r="G64" t="n">
-        <v>0.06049493277075371</v>
+        <v>0.03625441469738312</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2772,29 +2772,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0.02, 0.02, 0.08]</t>
+          <t>[-0.02, -0.09, -0.12]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.06409576828680857</v>
+        <v>0.08364598540141008</v>
       </c>
       <c r="G65" t="n">
-        <v>0.05794753381897776</v>
+        <v>0.07339884169585782</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2810,29 +2810,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0.0, 0.06, 0.02]</t>
+          <t>[-0.07, -0.1, -0.07]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[0.1, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.06603339405022904</v>
+        <v>0.0804308075034561</v>
       </c>
       <c r="G66" t="n">
-        <v>0.05728492291795353</v>
+        <v>0.07930679718505751</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2848,17 +2848,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0.16, 0.12, 0.2]</t>
+          <t>[-0.03, -0.01, -0.04]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.1624197734563818</v>
+        <v>0.03079432606908427</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1586955916764214</v>
+        <v>0.02666530019328991</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2886,17 +2886,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[-0.03, 0.04, 0.03]</t>
+          <t>[0.03, -0.01, 0.01]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.03446478306006705</v>
+        <v>0.01776011689746746</v>
       </c>
       <c r="G68" t="n">
-        <v>0.03410433579108158</v>
+        <v>0.01515770912953888</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2924,17 +2924,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0.08, 0.06, 0.11]</t>
+          <t>[-0.04, -0.02, -0.01]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.08372401296444049</v>
+        <v>0.02428653712417306</v>
       </c>
       <c r="G69" t="n">
-        <v>0.08193386602224169</v>
+        <v>0.02142179195103556</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2962,17 +2962,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[-0.01, 0.03, 0.01]</t>
+          <t>[0.02, 0.03, 0.07]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.01779470984843827</v>
+        <v>0.04337341695057196</v>
       </c>
       <c r="G70" t="n">
-        <v>0.01552241482970592</v>
+        <v>0.0376751061207476</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3000,17 +3000,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[0.04, 0.02, -0.05]</t>
+          <t>[0.01, 0.05, 0.02]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.03854038096053812</v>
+        <v>0.03076987718372728</v>
       </c>
       <c r="G71" t="n">
-        <v>0.03625441469738312</v>
+        <v>0.02560453439056513</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3038,32 +3038,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[57.87, 190.12, 84.74]</t>
+          <t>[29.76, 29.66, 24.91]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>[4.6, 6.5, 63.19]</t>
+          <t>[3.3, 4.3, 4.9]</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>111.0843263157193</v>
+        <v>24.10845076733633</v>
       </c>
       <c r="G72" t="n">
-        <v>86.14910804322125</v>
+        <v>23.94342172284768</v>
       </c>
       <c r="H72" t="n">
-        <v>1339.045783304044</v>
+        <v>599.9877092326735</v>
       </c>
     </row>
     <row r="73">
@@ -3074,32 +3074,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[100.21, 44.88, 85.55]</t>
+          <t>[17.27, 14.56, 18.7]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>[6.5, 63.19, 117.1]</t>
+          <t>[4.3, 4.9, 5.5]</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>58.05714894267639</v>
+        <v>12.05088634682095</v>
       </c>
       <c r="G73" t="n">
-        <v>47.85684230145582</v>
+        <v>11.94157959876802</v>
       </c>
       <c r="H73" t="n">
-        <v>499.192251950468</v>
+        <v>246.2258443728995</v>
       </c>
     </row>
     <row r="74">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[18.94, 37.07, 13.25]</t>
+          <t>[9.84, 12.79, 23.89]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>[63.19, 117.1, 3.5]</t>
+          <t>[4.9, 5.5, 29.7]</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>53.09657245759671</v>
+        <v>6.091877273438831</v>
       </c>
       <c r="G74" t="n">
-        <v>44.67556446133679</v>
+        <v>6.014270056770411</v>
       </c>
       <c r="H74" t="n">
-        <v>138.9435666951393</v>
+        <v>84.32034849839481</v>
       </c>
     </row>
     <row r="75">
@@ -3146,32 +3146,32 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[56.26, 20.31, 21.31]</t>
+          <t>[10.43, 19.67, 4.16]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>[117.1, 3.5, 4.3]</t>
+          <t>[5.5, 29.7, 3.8]</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>37.73953269188841</v>
+        <v>6.453979373603195</v>
       </c>
       <c r="G75" t="n">
-        <v>31.55149937703046</v>
+        <v>5.104698463072164</v>
       </c>
       <c r="H75" t="n">
-        <v>309.2711073918196</v>
+        <v>44.26853174857213</v>
       </c>
     </row>
     <row r="76">
@@ -3182,32 +3182,32 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[25.02, 26.05, 32.26]</t>
+          <t>[16.35, 3.34, 11.55]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>[3.5, 4.3, 76.7]</t>
+          <t>[29.7, 3.8, 5.3]</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>31.15187025481764</v>
+        <v>8.51459957470904</v>
       </c>
       <c r="G76" t="n">
-        <v>29.23767963117372</v>
+        <v>6.687392357858767</v>
       </c>
       <c r="H76" t="n">
-        <v>392.8780495597083</v>
+        <v>58.34683858488619</v>
       </c>
     </row>
     <row r="77">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[15.95, 19.97, 25.98]</t>
+          <t>[4.15, 13.88, 10.25]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>[4.3, 76.7, 3.3]</t>
+          <t>[3.8, 5.3, 2.7]</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>35.91007267962124</v>
+        <v>6.60027552535318</v>
       </c>
       <c r="G77" t="n">
-        <v>30.35459472104276</v>
+        <v>5.493294084620667</v>
       </c>
       <c r="H77" t="n">
-        <v>344.081952556426</v>
+        <v>150.2325226086536</v>
       </c>
     </row>
     <row r="78">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[13.76, 18.09, 18.14]</t>
+          <t>[13.58, 10.02, 20.17]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>[76.7, 3.3, 4.3]</t>
+          <t>[5.3, 2.7, 4.8]</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>38.17210022993438</v>
+        <v>10.93162307575566</v>
       </c>
       <c r="G78" t="n">
-        <v>30.52270479570753</v>
+        <v>10.32443282073989</v>
       </c>
       <c r="H78" t="n">
-        <v>284.0427105155687</v>
+        <v>249.2077468987576</v>
       </c>
     </row>
     <row r="79">
@@ -3290,32 +3290,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[29.76, 29.66, 24.91]</t>
+          <t>[7.64, 15.66, 3.32]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>[3.3, 4.3, 4.9]</t>
+          <t>[2.7, 4.8, 3.6]</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>24.10845076733633</v>
+        <v>6.888293795394177</v>
       </c>
       <c r="G79" t="n">
-        <v>23.94342172284768</v>
+        <v>5.358052050833458</v>
       </c>
       <c r="H79" t="n">
-        <v>599.9877092326735</v>
+        <v>138.9615676749423</v>
       </c>
     </row>
     <row r="80">
@@ -3326,32 +3326,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[17.27, 14.56, 18.7]</t>
+          <t>[11.92, 2.36, 2.76]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>[4.3, 4.9, 5.5]</t>
+          <t>[4.8, 3.6, 4.3]</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>12.05088634682095</v>
+        <v>4.26691408835182</v>
       </c>
       <c r="G80" t="n">
-        <v>11.94157959876802</v>
+        <v>3.300280822238612</v>
       </c>
       <c r="H80" t="n">
-        <v>246.2258443728995</v>
+        <v>72.86251094970181</v>
       </c>
     </row>
     <row r="81">
@@ -3362,32 +3362,32 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[9.84, 12.79, 23.89]</t>
+          <t>[1.63, 1.95, 4.29]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>[4.9, 5.5, 29.7]</t>
+          <t>[3.6, 4.3, 4.0]</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>6.091877273438831</v>
+        <v>1.781485892745408</v>
       </c>
       <c r="G81" t="n">
-        <v>6.014270056770411</v>
+        <v>1.539405656683994</v>
       </c>
       <c r="H81" t="n">
-        <v>84.32034849839481</v>
+        <v>38.94500213694451</v>
       </c>
     </row>
     <row r="82">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[951.04, 1107.33, 931.21]</t>
+          <t>[1130.66, 1805.39, 1433.88]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[1595.03, 1629.31, 1289.81]</t>
+          <t>[1658.56, 1816.86, 2029.92]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>521.4668947543604</v>
+        <v>459.7403717773432</v>
       </c>
       <c r="G82" t="n">
-        <v>508.1910598066402</v>
+        <v>378.47299002013</v>
       </c>
       <c r="H82" t="n">
-        <v>33.40480030334518</v>
+        <v>20.60778315404368</v>
       </c>
     </row>
     <row r="83">
@@ -3434,32 +3434,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[1384.13, 1161.53, 1664.05]</t>
+          <t>[2127.87, 1687.55, 1979.36]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[1629.31, 1289.81, 1888.54]</t>
+          <t>[1816.86, 2029.92, 1865.53]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>205.7224437024055</v>
+        <v>275.0150386984216</v>
       </c>
       <c r="G83" t="n">
-        <v>199.3177479015837</v>
+        <v>255.7366191898552</v>
       </c>
       <c r="H83" t="n">
-        <v>12.29365798222812</v>
+        <v>13.36197896111406</v>
       </c>
     </row>
     <row r="84">
@@ -3470,32 +3470,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[1246.47, 1784.43, 2041.45]</t>
+          <t>[1576.88, 1850.88, 2354.45]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[1289.81, 1888.54, 1709.14]</t>
+          <t>[2029.92, 1865.53, 2167.03]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>202.6080904955593</v>
+        <v>283.1865656286291</v>
       </c>
       <c r="G84" t="n">
-        <v>159.9207879436383</v>
+        <v>218.3671423023294</v>
       </c>
       <c r="H84" t="n">
-        <v>9.438712752270295</v>
+        <v>10.58390086270136</v>
       </c>
     </row>
     <row r="85">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[1811.02, 2071.57, 2039.04]</t>
+          <t>[2061.78, 2620.05, 1463.94]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[1888.54, 1709.14, 1555.1]</t>
+          <t>[1865.53, 2167.03, 1983.67]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>351.9268554768524</v>
+        <v>413.8682599477151</v>
       </c>
       <c r="G85" t="n">
-        <v>307.9603380963331</v>
+        <v>389.6661397468993</v>
       </c>
       <c r="H85" t="n">
-        <v>18.80972729962829</v>
+        <v>19.20841384604621</v>
       </c>
     </row>
     <row r="86">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[2109.33, 2075.77, 1649.76]</t>
+          <t>[2510.47, 1403.21, 1607.48]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[1709.14, 1555.1, 1561.05]</t>
+          <t>[2167.03, 1983.67, 1817.65]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>382.5882651919259</v>
+        <v>407.8643779796502</v>
       </c>
       <c r="G86" t="n">
-        <v>336.5245068114029</v>
+        <v>378.0250895310672</v>
       </c>
       <c r="H86" t="n">
-        <v>20.85968743209574</v>
+        <v>18.89111195693076</v>
       </c>
     </row>
     <row r="87">
@@ -3578,32 +3578,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[1896.2, 1508.32, 1168.69]</t>
+          <t>[1317.86, 1510.59, 1259.44]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[1555.1, 1561.05, 1658.56]</t>
+          <t>[1983.67, 1817.65, 2596.07]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>345.9752940614373</v>
+        <v>880.1860828132068</v>
       </c>
       <c r="G87" t="n">
-        <v>294.5652813916064</v>
+        <v>769.8369733337937</v>
       </c>
       <c r="H87" t="n">
-        <v>18.2825815058338</v>
+        <v>33.98167068823492</v>
       </c>
     </row>
     <row r="88">
@@ -3614,32 +3614,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[1384.89, 1073.83, 1715.47]</t>
+          <t>[1800.47, 1498.87, 2147.32]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[1561.05, 1658.56, 1816.86]</t>
+          <t>[1817.65, 2596.07, 1968.29]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>357.4052251051136</v>
+        <v>641.9209215174154</v>
       </c>
       <c r="G88" t="n">
-        <v>287.4230958684452</v>
+        <v>431.1348293470544</v>
       </c>
       <c r="H88" t="n">
-        <v>17.37328582145951</v>
+        <v>17.4348394536127</v>
       </c>
     </row>
     <row r="89">
@@ -3650,32 +3650,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[1130.66, 1805.39, 1433.88]</t>
+          <t>[1505.26, 2155.92, 2405.19]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[1658.56, 1816.86, 2029.92]</t>
+          <t>[2596.07, 1968.29, 1939.64]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>459.7403717773432</v>
+        <v>693.2555993739774</v>
       </c>
       <c r="G89" t="n">
-        <v>378.47299002013</v>
+        <v>581.3286758860844</v>
       </c>
       <c r="H89" t="n">
-        <v>20.60778315404368</v>
+        <v>25.18400937651641</v>
       </c>
     </row>
     <row r="90">
@@ -3686,32 +3686,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[2127.87, 1687.55, 1979.36]</t>
+          <t>[2727.53, 3036.25, 2955.95]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[1816.86, 2029.92, 1865.53]</t>
+          <t>[1968.29, 1939.64, 1631.96]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>275.0150386984216</v>
+        <v>1085.042984803092</v>
       </c>
       <c r="G90" t="n">
-        <v>255.7366191898552</v>
+        <v>1059.947516534685</v>
       </c>
       <c r="H90" t="n">
-        <v>13.36197896111406</v>
+        <v>58.74644025165229</v>
       </c>
     </row>
     <row r="91">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[1576.88, 1850.88, 2354.45]</t>
+          <t>[2638.49, 2570.78, 2087.22]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[2029.92, 1865.53, 2167.03]</t>
+          <t>[1939.64, 1631.96, 1759.46]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>283.1865656286291</v>
+        <v>701.7147150416949</v>
       </c>
       <c r="G91" t="n">
-        <v>218.3671423023294</v>
+        <v>655.1447052296004</v>
       </c>
       <c r="H91" t="n">
-        <v>10.58390086270136</v>
+        <v>37.3952344581638</v>
       </c>
     </row>
     <row r="92">
@@ -3758,32 +3758,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[1046.67, 896.12, 785.74]</t>
+          <t>[1089.58, 1084.69, 1041.53]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[1106.81, 962.8, 815.43]</t>
+          <t>[1035.3, 960.03, 1059.99]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>54.60193965579982</v>
+        <v>79.22059687495208</v>
       </c>
       <c r="G92" t="n">
-        <v>52.16844254845375</v>
+        <v>65.80122949751278</v>
       </c>
       <c r="H92" t="n">
-        <v>5.33327743311483</v>
+        <v>6.656610055440233</v>
       </c>
     </row>
     <row r="93">
@@ -3794,32 +3794,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[928.85, 814.08, 879.61]</t>
+          <t>[1050.38, 1008.85, 1207.63]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[962.8, 815.43, 1176.48]</t>
+          <t>[960.03, 1059.99, 1226.25]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>172.5186026449313</v>
+        <v>60.89755520435161</v>
       </c>
       <c r="G93" t="n">
-        <v>110.7257651363264</v>
+        <v>53.37132621925449</v>
       </c>
       <c r="H93" t="n">
-        <v>9.642070332407481</v>
+        <v>5.251518924571904</v>
       </c>
     </row>
     <row r="94">
@@ -3830,32 +3830,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[832.96, 899.85, 953.45]</t>
+          <t>[953.54, 1142.01, 1570.09]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[815.43, 1176.48, 1135.85]</t>
+          <t>[1059.99, 1226.25, 991.03]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>191.5741798601871</v>
+        <v>343.3836636084322</v>
       </c>
       <c r="G94" t="n">
-        <v>158.8530098082719</v>
+        <v>256.5830361533148</v>
       </c>
       <c r="H94" t="n">
-        <v>13.90715630439111</v>
+        <v>25.11408789842773</v>
       </c>
     </row>
     <row r="95">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[887.73, 940.72, 1174.79]</t>
+          <t>[1220.27, 1676.67, 1268.15]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[1176.48, 1135.85, 902.53]</t>
+          <t>[1226.25, 991.03, 972.64]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>255.329774534141</v>
+        <v>431.0673251539042</v>
       </c>
       <c r="G95" t="n">
-        <v>252.0482500217103</v>
+        <v>329.0423693270051</v>
       </c>
       <c r="H95" t="n">
-        <v>23.96312980694281</v>
+        <v>33.35138163059674</v>
       </c>
     </row>
     <row r="96">
@@ -3902,32 +3902,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[1125.7, 1403.61, 967.65]</t>
+          <t>[1681.66, 1271.93, 1088.96]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[1135.85, 902.53, 1132.8]</t>
+          <t>[991.03, 972.64, 1047.88]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>304.6636069027698</v>
+        <v>435.215646270956</v>
       </c>
       <c r="G96" t="n">
-        <v>225.4592720016524</v>
+        <v>343.6687266271167</v>
       </c>
       <c r="H96" t="n">
-        <v>23.6639432983065</v>
+        <v>34.79330512134575</v>
       </c>
     </row>
     <row r="97">
@@ -3938,32 +3938,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[1411.61, 973.15, 1097.18]</t>
+          <t>[913.84, 784.47, 686.2]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[902.53, 1132.8, 1035.3]</t>
+          <t>[972.64, 1047.88, 1179.17]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>310.0961827131459</v>
+        <v>324.4794761733957</v>
       </c>
       <c r="G97" t="n">
-        <v>243.5364317199843</v>
+        <v>271.7271678803485</v>
       </c>
       <c r="H97" t="n">
-        <v>25.49208012455399</v>
+        <v>24.32984145520466</v>
       </c>
     </row>
     <row r="98">
@@ -3974,32 +3974,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[732.3, 827.72, 826.03]</t>
+          <t>[816.01, 713.52, 794.43]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[1132.8, 1035.3, 960.03]</t>
+          <t>[1047.88, 1179.17, 989.24]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>271.6891180371815</v>
+        <v>320.701875912437</v>
       </c>
       <c r="G98" t="n">
-        <v>247.3595528133872</v>
+        <v>297.4452438765666</v>
       </c>
       <c r="H98" t="n">
-        <v>23.12096119364021</v>
+        <v>27.10352791525363</v>
       </c>
     </row>
     <row r="99">
@@ -4010,32 +4010,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[1089.58, 1084.69, 1041.53]</t>
+          <t>[834.11, 927.51, 973.64]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[1035.3, 960.03, 1059.99]</t>
+          <t>[1179.17, 989.24, 1101.94]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>79.22059687495208</v>
+        <v>215.5153766807709</v>
       </c>
       <c r="G99" t="n">
-        <v>65.80122949751278</v>
+        <v>178.365574572317</v>
       </c>
       <c r="H99" t="n">
-        <v>6.656610055440233</v>
+        <v>15.71561103207888</v>
       </c>
     </row>
     <row r="100">
@@ -4046,32 +4046,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[1050.38, 1008.85, 1207.63]</t>
+          <t>[1152.57, 1207.84, 1438.98]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[960.03, 1059.99, 1226.25]</t>
+          <t>[989.24, 1101.94, 1008.55]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>60.89755520435161</v>
+        <v>272.7417424820998</v>
       </c>
       <c r="G100" t="n">
-        <v>53.37132621925449</v>
+        <v>233.2214103088253</v>
       </c>
       <c r="H100" t="n">
-        <v>5.251518924571904</v>
+        <v>22.93315851333363</v>
       </c>
     </row>
     <row r="101">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[953.54, 1142.01, 1570.09]</t>
+          <t>[1097.45, 1308.47, 958.12]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[1059.99, 1226.25, 991.03]</t>
+          <t>[1101.94, 1008.55, 912.93]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>343.3836636084322</v>
+        <v>175.1336756876578</v>
       </c>
       <c r="G101" t="n">
-        <v>256.5830361533148</v>
+        <v>116.533831975271</v>
       </c>
       <c r="H101" t="n">
-        <v>25.11408789842773</v>
+        <v>11.69847754815309</v>
       </c>
     </row>
     <row r="102">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[845.31, 820.98, 962.72]</t>
+          <t>[849.02, 944.14, 944.94]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[882.31, 909.42, 1155.23]</t>
+          <t>[977.18, 1036.95, 1137.79]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>124.1660260794651</v>
+        <v>144.0228397781938</v>
       </c>
       <c r="G102" t="n">
-        <v>105.983399403247</v>
+        <v>137.9375020962152</v>
       </c>
       <c r="H102" t="n">
-        <v>10.19419729797381</v>
+        <v>13.00479859056992</v>
       </c>
     </row>
     <row r="103">
@@ -4154,32 +4154,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[832.85, 976.64, 941.87]</t>
+          <t>[988.12, 988.59, 964.56]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[909.42, 1155.23, 972.4]</t>
+          <t>[1036.95, 1137.79, 934.12]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>113.5630253708541</v>
+        <v>92.32661712411227</v>
       </c>
       <c r="G103" t="n">
-        <v>95.2298992161443</v>
+        <v>76.15713290412903</v>
       </c>
       <c r="H103" t="n">
-        <v>9.006193591831995</v>
+        <v>7.026967441786279</v>
       </c>
     </row>
     <row r="104">
@@ -4190,32 +4190,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[1006.1, 970.04, 848.21]</t>
+          <t>[1004.1, 979.55, 1156.77]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[1155.23, 972.4, 1034.85]</t>
+          <t>[1137.79, 934.12, 1132.22]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>137.9378652629882</v>
+        <v>82.74379532143217</v>
       </c>
       <c r="G104" t="n">
-        <v>112.7114146768529</v>
+        <v>67.88939348585343</v>
       </c>
       <c r="H104" t="n">
-        <v>10.39589807575732</v>
+        <v>6.260518707742481</v>
       </c>
     </row>
     <row r="105">
@@ -4226,32 +4226,32 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[1018.46, 890.26, 1033.1]</t>
+          <t>[1020.64, 1204.85, 965.57]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[972.4, 1034.85, 894.67]</t>
+          <t>[934.12, 1132.22, 1000.83]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>118.5897791893979</v>
+        <v>68.32217762596721</v>
       </c>
       <c r="G105" t="n">
-        <v>109.6940392997935</v>
+        <v>64.80332045388775</v>
       </c>
       <c r="H105" t="n">
-        <v>11.39390488124746</v>
+        <v>6.400015259470051</v>
       </c>
     </row>
     <row r="106">
@@ -4262,32 +4262,32 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[875.6, 1016.29, 966.95]</t>
+          <t>[1170.26, 938.3, 915.92]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[1034.85, 894.67, 859.41]</t>
+          <t>[1132.22, 1000.83, 892.11]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>131.2997762299481</v>
+        <v>44.43601119004637</v>
       </c>
       <c r="G106" t="n">
-        <v>129.4725491984427</v>
+        <v>41.45904042440785</v>
       </c>
       <c r="H106" t="n">
-        <v>13.8321973221918</v>
+        <v>4.092087138008589</v>
       </c>
     </row>
     <row r="107">
@@ -4298,32 +4298,32 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[1077.54, 1024.67, 938.34]</t>
+          <t>[928.37, 906.21, 1070.5]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[894.67, 859.41, 977.18]</t>
+          <t>[1000.83, 892.11, 877.74]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>144.0602790144557</v>
+        <v>119.1728002654135</v>
       </c>
       <c r="G107" t="n">
-        <v>128.9902493782507</v>
+        <v>93.10837747446244</v>
       </c>
       <c r="H107" t="n">
-        <v>14.54805080647736</v>
+        <v>10.26066214483078</v>
       </c>
     </row>
     <row r="108">
@@ -4334,32 +4334,32 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[961.16, 880.67, 979.05]</t>
+          <t>[928.38, 1096.45, 1042.17]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[859.41, 977.18, 1036.95]</t>
+          <t>[892.11, 877.74, 1046.8]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>87.59864271201931</v>
+        <v>128.0240570985692</v>
       </c>
       <c r="G108" t="n">
-        <v>85.38834709434764</v>
+        <v>86.53657424579849</v>
       </c>
       <c r="H108" t="n">
-        <v>9.100040612885698</v>
+        <v>9.808430900349329</v>
       </c>
     </row>
     <row r="109">
@@ -4370,32 +4370,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[849.02, 944.14, 944.94]</t>
+          <t>[1082.56, 1029.11, 917.15]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[977.18, 1036.95, 1137.79]</t>
+          <t>[877.74, 1046.8, 920.13]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>144.0228397781938</v>
+        <v>118.7077632613451</v>
       </c>
       <c r="G109" t="n">
-        <v>137.9375020962152</v>
+        <v>75.16330324749606</v>
       </c>
       <c r="H109" t="n">
-        <v>13.00479859056992</v>
+        <v>8.449580465193298</v>
       </c>
     </row>
     <row r="110">
@@ -4406,32 +4406,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[988.12, 988.59, 964.56]</t>
+          <t>[962.62, 858.44, 967.72]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[1036.95, 1137.79, 934.12]</t>
+          <t>[1046.8, 920.13, 1090.89]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>92.32661712411227</v>
+        <v>93.20463951121641</v>
       </c>
       <c r="G110" t="n">
-        <v>76.15713290412903</v>
+        <v>89.67764565089492</v>
       </c>
       <c r="H110" t="n">
-        <v>7.026967441786279</v>
+        <v>8.678750311498</v>
       </c>
     </row>
     <row r="111">
@@ -4442,32 +4442,32 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[1004.1, 979.55, 1156.77]</t>
+          <t>[881.95, 994.0, 946.68]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[1137.79, 934.12, 1132.22]</t>
+          <t>[920.13, 1090.89, 866.57]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>82.74379532143217</v>
+        <v>75.85477110735035</v>
       </c>
       <c r="G111" t="n">
-        <v>67.88939348585343</v>
+        <v>71.72527116539236</v>
       </c>
       <c r="H111" t="n">
-        <v>6.260518707742481</v>
+        <v>7.425083087989254</v>
       </c>
     </row>
     <row r="112">
@@ -4478,32 +4478,32 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[942.7, 934.55, 930.65]</t>
+          <t>[699.88, 772.31, 854.38]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>[1358.71, 1174.79, 1119.53]</t>
+          <t>[1466.16, 1237.16, 1259.01]</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>298.0249691845715</v>
+        <v>567.7451206946557</v>
       </c>
       <c r="G112" t="n">
-        <v>281.710057314169</v>
+        <v>545.2553849620613</v>
       </c>
       <c r="H112" t="n">
-        <v>22.64631948533864</v>
+        <v>40.65919562458433</v>
       </c>
     </row>
     <row r="113">
@@ -4514,32 +4514,32 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[1082.39, 1075.96, 1005.78]</t>
+          <t>[994.89, 1098.11, 1128.06]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>[1174.79, 1119.53, 1112.85]</t>
+          <t>[1237.16, 1259.01, 1269.69]</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>85.43814537594427</v>
+        <v>186.7647827950169</v>
       </c>
       <c r="G113" t="n">
-        <v>81.01199948755944</v>
+        <v>181.6005969404805</v>
       </c>
       <c r="H113" t="n">
-        <v>7.12598152686771</v>
+        <v>14.50582373711946</v>
       </c>
     </row>
     <row r="114">
@@ -4550,32 +4550,32 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[1107.2, 1034.75, 1035.95]</t>
+          <t>[1175.21, 1206.66, 2052.12]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[1119.53, 1112.85, 1039.56]</t>
+          <t>[1259.01, 1269.69, 1539.94]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>45.6987359215216</v>
+        <v>301.8418237889494</v>
       </c>
       <c r="G114" t="n">
-        <v>31.34637686119951</v>
+        <v>219.6695143305436</v>
       </c>
       <c r="H114" t="n">
-        <v>2.822183183419229</v>
+        <v>14.95993967495953</v>
       </c>
     </row>
     <row r="115">
@@ -4586,32 +4586,32 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[1038.75, 1039.98, 1078.68]</t>
+          <t>[1233.77, 2097.75, 1209.49]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[1112.85, 1039.56, 615.58]</t>
+          <t>[1269.69, 1539.94, 1481.59]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>270.7732828258455</v>
+        <v>358.9245944260484</v>
       </c>
       <c r="G115" t="n">
-        <v>179.2068656909229</v>
+        <v>288.6087480464502</v>
       </c>
       <c r="H115" t="n">
-        <v>27.30969552634502</v>
+        <v>19.13899491149824</v>
       </c>
     </row>
     <row r="116">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[1065.07, 1104.49, 894.44]</t>
+          <t>[2117.34, 1220.62, 1191.12]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[1039.56, 615.58, 545.87]</t>
+          <t>[1539.94, 1481.59, 1377.83]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>346.9817122225091</v>
+        <v>381.3819248123838</v>
       </c>
       <c r="G116" t="n">
-        <v>287.665373251962</v>
+        <v>341.6941567886392</v>
       </c>
       <c r="H116" t="n">
-        <v>48.57776048134162</v>
+        <v>22.88678635565807</v>
       </c>
     </row>
     <row r="117">
@@ -4658,32 +4658,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[1095.2, 887.01, 955.04]</t>
+          <t>[1107.09, 1081.23, 1070.44]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>[615.58, 545.87, 1466.16]</t>
+          <t>[1481.59, 1377.83, 1435.98]</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>450.0551350581115</v>
+        <v>347.2946187478091</v>
       </c>
       <c r="G117" t="n">
-        <v>443.957531268501</v>
+        <v>345.5460399296355</v>
       </c>
       <c r="H117" t="n">
-        <v>58.42280771235392</v>
+        <v>24.08637771931451</v>
       </c>
     </row>
     <row r="118">
@@ -4694,32 +4694,32 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[727.63, 784.84, 865.15]</t>
+          <t>[1180.41, 1167.73, 1097.58]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>[545.87, 1466.16, 1237.16]</t>
+          <t>[1377.83, 1435.98, 1111.97]</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>460.3012319789489</v>
+        <v>192.4731826240136</v>
       </c>
       <c r="G118" t="n">
-        <v>411.6983467102044</v>
+        <v>160.0179881160344</v>
       </c>
       <c r="H118" t="n">
-        <v>36.61232529312995</v>
+        <v>11.43419632711139</v>
       </c>
     </row>
     <row r="119">
@@ -4730,32 +4730,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[699.88, 772.31, 854.38]</t>
+          <t>[1224.13, 1149.95, 1142.5]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>[1466.16, 1237.16, 1259.01]</t>
+          <t>[1435.98, 1111.97, 1062.91]</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>567.7451206946557</v>
+        <v>132.4851386102422</v>
       </c>
       <c r="G119" t="n">
-        <v>545.2553849620613</v>
+        <v>109.8059531718188</v>
       </c>
       <c r="H119" t="n">
-        <v>40.65919562458433</v>
+        <v>8.552114159601693</v>
       </c>
     </row>
     <row r="120">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[994.89, 1098.11, 1128.06]</t>
+          <t>[1209.17, 1200.57, 1176.04]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>[1237.16, 1259.01, 1269.69]</t>
+          <t>[1111.97, 1062.91, 988.78]</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>186.7647827950169</v>
+        <v>145.4502130564472</v>
       </c>
       <c r="G120" t="n">
-        <v>181.6005969404805</v>
+        <v>140.7099164545446</v>
       </c>
       <c r="H120" t="n">
-        <v>14.50582373711946</v>
+        <v>13.54396880041343</v>
       </c>
     </row>
     <row r="121">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[1175.21, 1206.66, 2052.12]</t>
+          <t>[1169.56, 1145.67, 935.4]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[1259.01, 1269.69, 1539.94]</t>
+          <t>[1062.91, 988.78, 1083.18]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>301.8418237889494</v>
+        <v>138.8381862901044</v>
       </c>
       <c r="G121" t="n">
-        <v>219.6695143305436</v>
+        <v>137.1072613081751</v>
       </c>
       <c r="H121" t="n">
-        <v>14.95993967495953</v>
+        <v>13.18136808011535</v>
       </c>
     </row>
     <row r="122">
@@ -4838,32 +4838,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[1.7, 1.54, 1.57]</t>
+          <t>[3.09, 4.43, 4.64]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[1.5, 1.0, 4.88]</t>
+          <t>[1.2, 31.41, 2.1]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1.941359743458038</v>
+        <v>15.68342640451619</v>
       </c>
       <c r="G122" t="n">
-        <v>1.350835697033197</v>
+        <v>10.46925543077163</v>
       </c>
       <c r="H122" t="n">
-        <v>45.00792484158506</v>
+        <v>121.3943826926182</v>
       </c>
     </row>
     <row r="123">
@@ -4874,32 +4874,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[1.52, 1.55, 1.4]</t>
+          <t>[3.93, 4.06, 3.91]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[1.0, 4.88, 4.53]</t>
+          <t>[31.41, 2.1, 1.6]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>2.653903241461201</v>
+        <v>15.96203416033279</v>
       </c>
       <c r="G123" t="n">
-        <v>2.326454260862314</v>
+        <v>10.58252754235378</v>
       </c>
       <c r="H123" t="n">
-        <v>63.21217340139334</v>
+        <v>108.3296999407196</v>
       </c>
     </row>
     <row r="124">
@@ -4910,32 +4910,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[1.52, 1.37, 1.34]</t>
+          <t>[5.62, 5.36, 30.85]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[4.88, 4.53, 10.26]</t>
+          <t>[2.1, 1.6, 41.06]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5.79464632409285</v>
+        <v>6.603299285514792</v>
       </c>
       <c r="G124" t="n">
-        <v>5.14391844783313</v>
+        <v>5.830201186644953</v>
       </c>
       <c r="H124" t="n">
-        <v>75.14357424189478</v>
+        <v>142.4779350842081</v>
       </c>
     </row>
     <row r="125">
@@ -4946,32 +4946,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[1.52, 1.47, 1.75]</t>
+          <t>[4.5, 27.14, 2.78]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[4.53, 10.26, 0.8]</t>
+          <t>[1.6, 41.06, 1.4]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>5.390735006903495</v>
+        <v>8.246727778204026</v>
       </c>
       <c r="G125" t="n">
-        <v>4.247762238612816</v>
+        <v>6.068106445671927</v>
       </c>
       <c r="H125" t="n">
-        <v>90.18264572060217</v>
+        <v>104.7381933970721</v>
       </c>
     </row>
     <row r="126">
@@ -4982,32 +4982,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[1.65, 1.93, 3.72]</t>
+          <t>[25.17, 2.43, 1.99]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[10.26, 0.8, 17.82]</t>
+          <t>[41.06, 1.4, 10.95]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>9.559403361681847</v>
+        <v>10.54785699525587</v>
       </c>
       <c r="G126" t="n">
-        <v>7.946088796722528</v>
+        <v>8.626496702351863</v>
       </c>
       <c r="H126" t="n">
-        <v>101.4218282755005</v>
+        <v>64.73537200529232</v>
       </c>
     </row>
     <row r="127">
@@ -5018,32 +5018,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[2.63, 4.78, 2.92]</t>
+          <t>[2.57, 2.11, 4.43]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[0.8, 17.82, 1.2]</t>
+          <t>[1.4, 10.95, 5.3]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>7.665135025012014</v>
+        <v>5.173981233019695</v>
       </c>
       <c r="G127" t="n">
-        <v>5.529061204101786</v>
+        <v>3.62661998597683</v>
       </c>
       <c r="H127" t="n">
-        <v>148.4604146786738</v>
+        <v>60.26053855805137</v>
       </c>
     </row>
     <row r="128">
@@ -5054,32 +5054,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[4.11, 2.41, 3.52]</t>
+          <t>[1.98, 4.25, 3.78]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[17.82, 1.2, 31.41]</t>
+          <t>[10.95, 5.3, 5.6]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>17.95584336857015</v>
+        <v>5.320343473330708</v>
       </c>
       <c r="G128" t="n">
-        <v>14.27040538574491</v>
+        <v>3.949116283938372</v>
       </c>
       <c r="H128" t="n">
-        <v>88.95376734422233</v>
+        <v>44.78368250128062</v>
       </c>
     </row>
     <row r="129">
@@ -5090,32 +5090,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[3.09, 4.43, 4.64]</t>
+          <t>[4.93, 4.39, 6.37]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[1.2, 31.41, 2.1]</t>
+          <t>[5.3, 5.6, 3.5]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>15.68342640451619</v>
+        <v>1.81135463011511</v>
       </c>
       <c r="G129" t="n">
-        <v>10.46925543077163</v>
+        <v>1.481971650981209</v>
       </c>
       <c r="H129" t="n">
-        <v>121.3943826926182</v>
+        <v>36.84705586259575</v>
       </c>
     </row>
     <row r="130">
@@ -5126,32 +5126,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[3.93, 4.06, 3.91]</t>
+          <t>[4.43, 6.43, 2.01]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[31.41, 2.1, 1.6]</t>
+          <t>[5.6, 3.5, 7.9]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>15.96203416033279</v>
+        <v>3.857679010072958</v>
       </c>
       <c r="G130" t="n">
-        <v>10.58252754235378</v>
+        <v>3.329518607456944</v>
       </c>
       <c r="H130" t="n">
-        <v>108.3296999407196</v>
+        <v>59.71611783766681</v>
       </c>
     </row>
     <row r="131">
@@ -5162,32 +5162,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[5.62, 5.36, 30.85]</t>
+          <t>[6.61, 2.06, 11.8]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[2.1, 1.6, 41.06]</t>
+          <t>[3.5, 7.9, 0.3]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>6.603299285514792</v>
+        <v>7.65710831531447</v>
       </c>
       <c r="G131" t="n">
-        <v>5.830201186644953</v>
+        <v>6.813610885660295</v>
       </c>
       <c r="H131" t="n">
-        <v>142.4779350842081</v>
+        <v>1331.606150961889</v>
       </c>
     </row>
     <row r="132">
@@ -5198,32 +5198,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[940.23, 907.89, 595.24]</t>
+          <t>[748.77, 991.63, 485.29]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[719.0, 599.01, 842.52]</t>
+          <t>[921.96, 379.6, 601.52]</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>261.7230444913129</v>
+        <v>373.3114023437826</v>
       </c>
       <c r="G132" t="n">
-        <v>259.1300985373738</v>
+        <v>300.4824857829955</v>
       </c>
       <c r="H132" t="n">
-        <v>37.22810562600704</v>
+        <v>66.4459217573125</v>
       </c>
     </row>
     <row r="133">
@@ -5234,32 +5234,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[788.16, 517.38, 505.09]</t>
+          <t>[1105.11, 540.37, 972.94]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>[599.01, 842.52, 855.84]</t>
+          <t>[379.6, 601.52, 808.27]</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>296.9392026518344</v>
+        <v>430.9779914662866</v>
       </c>
       <c r="G133" t="n">
-        <v>288.3458597324736</v>
+        <v>317.1092937312346</v>
       </c>
       <c r="H133" t="n">
-        <v>37.05038670823238</v>
+        <v>73.88805189399838</v>
       </c>
     </row>
     <row r="134">
@@ -5270,32 +5270,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[448.02, 437.94, 633.83]</t>
+          <t>[310.54, 562.25, 966.91]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>[842.52, 855.84, 710.09]</t>
+          <t>[601.52, 808.27, 754.21]</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>334.7060945767493</v>
+        <v>251.9518750385882</v>
       </c>
       <c r="G134" t="n">
-        <v>296.2187516821055</v>
+        <v>249.901848331572</v>
       </c>
       <c r="H134" t="n">
-        <v>35.46401076400793</v>
+        <v>35.67151707800041</v>
       </c>
     </row>
     <row r="135">
@@ -5306,32 +5306,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[609.12, 878.85, 797.65]</t>
+          <t>[790.37, 1354.79, 868.99]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[855.84, 710.09, 641.57]</t>
+          <t>[808.27, 754.21, 508.83]</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>194.6891472920953</v>
+        <v>404.4498221381366</v>
       </c>
       <c r="G135" t="n">
-        <v>190.5203646648289</v>
+        <v>326.2149972056852</v>
       </c>
       <c r="H135" t="n">
-        <v>25.640628130155</v>
+        <v>50.87590297462813</v>
       </c>
     </row>
     <row r="136">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[1050.49, 951.92, 704.18]</t>
+          <t>[1370.25, 878.83, 836.69]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>[710.09, 641.57, 667.37]</t>
+          <t>[754.21, 508.83, 427.6]</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>266.8013820733867</v>
+        <v>477.4096396205599</v>
       </c>
       <c r="G136" t="n">
-        <v>229.1888382681596</v>
+        <v>465.0426557076025</v>
       </c>
       <c r="H136" t="n">
-        <v>33.94258097969187</v>
+        <v>83.35546429314682</v>
       </c>
     </row>
     <row r="137">
@@ -5378,32 +5378,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[775.72, 574.79, 725.77]</t>
+          <t>[648.21, 618.65, 439.02]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[641.57, 667.37, 921.96]</t>
+          <t>[508.83, 427.6, 618.8]</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>147.2587171681955</v>
+        <v>171.5104433613206</v>
       </c>
       <c r="G137" t="n">
-        <v>140.97037577293</v>
+        <v>170.0695808461613</v>
       </c>
       <c r="H137" t="n">
-        <v>18.6868190530319</v>
+        <v>33.70827524043325</v>
       </c>
     </row>
     <row r="138">
@@ -5414,32 +5414,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[520.64, 657.99, 872.34]</t>
+          <t>[546.02, 387.85, 381.22]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>[667.37, 921.96, 379.6]</t>
+          <t>[427.6, 618.8, 1039.88]</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>333.6671832787217</v>
+        <v>408.7338989385087</v>
       </c>
       <c r="G138" t="n">
-        <v>301.1459961819914</v>
+        <v>336.0085991600814</v>
       </c>
       <c r="H138" t="n">
-        <v>60.14077683786216</v>
+        <v>42.78527902645513</v>
       </c>
     </row>
     <row r="139">
@@ -5450,32 +5450,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[748.77, 991.63, 485.29]</t>
+          <t>[341.94, 336.46, 461.94]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[921.96, 379.6, 601.52]</t>
+          <t>[618.8, 1039.88, 730.33]</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>373.3114023437826</v>
+        <v>463.1392771036244</v>
       </c>
       <c r="G139" t="n">
-        <v>300.4824857829955</v>
+        <v>416.2266128517167</v>
       </c>
       <c r="H139" t="n">
-        <v>66.4459217573125</v>
+        <v>49.71206071414089</v>
       </c>
     </row>
     <row r="140">
@@ -5486,32 +5486,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[1105.11, 540.37, 972.94]</t>
+          <t>[455.86, 624.28, 568.01]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[379.6, 601.52, 808.27]</t>
+          <t>[1039.88, 730.33, 876.72]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>430.9779914662866</v>
+        <v>386.2754034624103</v>
       </c>
       <c r="G140" t="n">
-        <v>317.1092937312346</v>
+        <v>332.9266758394864</v>
       </c>
       <c r="H140" t="n">
-        <v>73.88805189399838</v>
+        <v>35.2983591603339</v>
       </c>
     </row>
     <row r="141">
@@ -5522,32 +5522,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[310.54, 562.25, 966.91]</t>
+          <t>[954.19, 865.27, 662.9]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>[601.52, 808.27, 754.21]</t>
+          <t>[730.33, 876.72, 911.41]</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>251.9518750385882</v>
+        <v>193.2212191458108</v>
       </c>
       <c r="G141" t="n">
-        <v>249.901848331572</v>
+        <v>161.2748414993395</v>
       </c>
       <c r="H141" t="n">
-        <v>35.67151707800041</v>
+        <v>19.74168658530134</v>
       </c>
     </row>
     <row r="142">
@@ -5558,32 +5558,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[1923.28, 1834.87, 2043.51]</t>
+          <t>[1989.03, 1827.07, 1878.76]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[1722.4, 1693.8, 1936.9]</t>
+          <t>[1936.9, 1862.4, 1948.9]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>154.5124830029537</v>
+        <v>54.42332745261314</v>
       </c>
       <c r="G142" t="n">
-        <v>149.5236388918792</v>
+        <v>52.53503668892707</v>
       </c>
       <c r="H142" t="n">
-        <v>8.498724716141375</v>
+        <v>2.729217753604407</v>
       </c>
     </row>
     <row r="143">
@@ -5594,32 +5594,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[1834.79, 2044.05, 1873.5]</t>
+          <t>[1813.78, 1866.37, 1908.71]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[1693.8, 1936.9, 1862.4]</t>
+          <t>[1862.4, 1948.9, 2098.7]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>102.4393220428619</v>
+        <v>122.8428373357792</v>
       </c>
       <c r="G143" t="n">
-        <v>86.41232338476107</v>
+        <v>107.0461895945001</v>
       </c>
       <c r="H143" t="n">
-        <v>4.817254439339102</v>
+        <v>5.299326920910663</v>
       </c>
     </row>
     <row r="144">
@@ -5630,32 +5630,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[1989.03, 1827.07, 1878.76]</t>
+          <t>[1876.89, 1918.76, 2210.54]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[1936.9, 1862.4, 1948.9]</t>
+          <t>[1948.9, 2098.7, 2226.0]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>54.42332745261314</v>
+        <v>112.253519323979</v>
       </c>
       <c r="G144" t="n">
-        <v>52.53503668892707</v>
+        <v>89.13631345016309</v>
       </c>
       <c r="H144" t="n">
-        <v>2.729217753604407</v>
+        <v>4.321083189138611</v>
       </c>
     </row>
     <row r="145">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[1813.78, 1866.37, 1908.71]</t>
+          <t>[1930.4, 2223.04, 1787.61]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[1862.4, 1948.9, 2098.7]</t>
+          <t>[2098.7, 2226.0, 1879.2]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>122.8428373357792</v>
+        <v>110.6381836532593</v>
       </c>
       <c r="G145" t="n">
-        <v>107.0461895945001</v>
+        <v>87.61828185512506</v>
       </c>
       <c r="H145" t="n">
-        <v>5.299326920910663</v>
+        <v>4.342116807589063</v>
       </c>
     </row>
     <row r="146">
@@ -5702,1474 +5702,2026 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[1876.89, 1918.76, 2210.54]</t>
+          <t>[2257.48, 1812.68, 1813.09]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[1948.9, 2098.7, 2226.0]</t>
+          <t>[2226.0, 1879.2, 1683.5]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>112.253519323979</v>
+        <v>86.0425849862018</v>
       </c>
       <c r="G146" t="n">
-        <v>89.13631345016309</v>
+        <v>75.86537055751819</v>
       </c>
       <c r="H146" t="n">
-        <v>4.321083189138611</v>
+        <v>4.217315744397717</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[54.03, 46.21, 43.92]</t>
+          <t>[1812.62, 1812.99, 1956.19]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[254.0, 117.1, 13.8]</t>
+          <t>[1879.2, 1683.5, 1821.7]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>123.7228066058868</v>
+        <v>114.4406945272301</v>
       </c>
       <c r="G147" t="n">
-        <v>100.326415491383</v>
+        <v>110.1894198620164</v>
       </c>
       <c r="H147" t="n">
-        <v>119.1661447949275</v>
+        <v>6.205943103401301</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[191.9, 159.67, 51.57]</t>
+          <t>[1812.99, 1956.16, 1924.94]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[117.1, 13.8, 9.8]</t>
+          <t>[1683.5, 1821.7, 2239.8]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>97.6685852796453</v>
+        <v>211.3342303729749</v>
       </c>
       <c r="G148" t="n">
-        <v>87.47888616213265</v>
+        <v>192.9377270915449</v>
       </c>
       <c r="H148" t="n">
-        <v>515.6915392722557</v>
+        <v>9.710115863129143</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[43.92, 15.78, 7.46]</t>
+          <t>[1956.48, 1925.04, 1873.15]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[13.8, 9.8, 140.7]</t>
+          <t>[1821.7, 2239.8, 2224.7]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>78.94012893238023</v>
+        <v>283.3321621079392</v>
       </c>
       <c r="G149" t="n">
-        <v>56.4450000688012</v>
+        <v>267.0328660173602</v>
       </c>
       <c r="H149" t="n">
-        <v>124.6592732453018</v>
+        <v>12.41805714243719</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[4.41, 1.55, 3.87]</t>
+          <t>[1925.03, 1873.37, 1853.84]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[9.8, 140.7, 58.1]</t>
+          <t>[2239.8, 2224.7, 1720.7]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>86.27773862520745</v>
+        <v>282.9826196661786</v>
       </c>
       <c r="G150" t="n">
-        <v>66.25574537472711</v>
+        <v>266.4127825566736</v>
       </c>
       <c r="H150" t="n">
-        <v>82.41418570853503</v>
+        <v>12.52774134888324</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[3.85, 8.07, 61.93]</t>
+          <t>[1873.87, 1853.72, 1786.49]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[140.7, 58.1, 57.2]</t>
+          <t>[2224.7, 1720.7, 2036.8]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>84.17057282994763</v>
+        <v>260.4007047993348</v>
       </c>
       <c r="G151" t="n">
-        <v>63.86948796545486</v>
+        <v>244.7167023710691</v>
       </c>
       <c r="H151" t="n">
-        <v>63.87875399388688</v>
+        <v>11.92974538630416</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[9.21, 2.21, 0.67]</t>
+          <t>[43.92, 15.78, 7.46]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[0.0, 9.6, 3.1]</t>
+          <t>[13.8, 9.8, 140.7]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>6.959338326645778</v>
+        <v>78.94012893238023</v>
       </c>
       <c r="G152" t="n">
-        <v>6.341735078210703</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>56.4450000688012</v>
+      </c>
+      <c r="H152" t="n">
+        <v>124.6592732453018</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[-0.45, -0.69, -0.04]</t>
+          <t>[4.41, 1.55, 3.87]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[9.6, 3.1, 8.7]</t>
+          <t>[9.8, 140.7, 58.1]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>7.994035261088118</v>
+        <v>86.27773862520745</v>
       </c>
       <c r="G153" t="n">
-        <v>7.525786530170589</v>
+        <v>66.25574537472711</v>
       </c>
       <c r="H153" t="n">
-        <v>109.1216396547771</v>
+        <v>82.41418570853503</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[0.44, 3.17, 1.57]</t>
+          <t>[3.85, 8.07, 61.93]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[3.1, 8.7, 6.0]</t>
+          <t>[140.7, 58.1, 57.2]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>4.369651492111524</v>
+        <v>84.17057282994763</v>
       </c>
       <c r="G154" t="n">
-        <v>4.207316872546034</v>
+        <v>63.86948796545486</v>
       </c>
       <c r="H154" t="n">
-        <v>74.43496022895366</v>
+        <v>63.87875399388688</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[5.36, 2.86, 2.02]</t>
+          <t>[16.23, 128.88, 67.17]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[8.7, 6.0, 2.0]</t>
+          <t>[58.1, 57.2, 279.8]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2.648499101781298</v>
+        <v>131.7839760115838</v>
       </c>
       <c r="G155" t="n">
-        <v>2.16727569203226</v>
+        <v>108.7262778272349</v>
       </c>
       <c r="H155" t="n">
-        <v>30.55247677194352</v>
+        <v>91.12615759242111</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[3.74, 2.68, 11.22]</t>
+          <t>[128.89, 67.17, 27.78]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[6.0, 2.0, 12.6]</t>
+          <t>[57.2, 279.8, 3.9]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1.578869977049308</v>
+        <v>130.2830177816956</v>
       </c>
       <c r="G156" t="n">
-        <v>1.440862366725649</v>
+        <v>102.7334992588515</v>
       </c>
       <c r="H156" t="n">
-        <v>27.59037615843099</v>
+        <v>271.2406792237974</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[180.13, 136.23, 202.09]</t>
+          <t>[67.17, 27.78, 7.43]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[252.7, 362.73, 279.14]</t>
+          <t>[279.8, 3.9, 5.9]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>144.3418846832994</v>
+        <v>123.539087289006</v>
       </c>
       <c r="G157" t="n">
-        <v>125.3718827412352</v>
+        <v>79.34893011223737</v>
       </c>
       <c r="H157" t="n">
-        <v>39.58739747301829</v>
+        <v>238.1093344660165</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[159.62, 236.33, 266.89]</t>
+          <t>[27.78, 7.43, 107.71]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[362.73, 279.14, 309.56]</t>
+          <t>[3.9, 5.9, 124.4]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>122.3478657010029</v>
+        <v>16.8459552180369</v>
       </c>
       <c r="G158" t="n">
-        <v>96.19543972504279</v>
+        <v>14.03499493876777</v>
       </c>
       <c r="H158" t="n">
-        <v>28.37131800856931</v>
+        <v>217.2491820408623</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[345.73, 389.04, 423.46]</t>
+          <t>[7.43, 107.72, 200.24]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[279.14, 309.56, 261.9]</t>
+          <t>[5.9, 124.4, 280.2]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>110.836513435768</v>
+        <v>47.16870448084106</v>
       </c>
       <c r="G159" t="n">
-        <v>102.5445745006035</v>
+        <v>32.7253439008927</v>
       </c>
       <c r="H159" t="n">
-        <v>37.0732361490485</v>
+        <v>22.62427384178407</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[352.26, 383.74, 298.33]</t>
+          <t>[107.72, 200.2, 90.75]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[309.56, 261.9, 145.4]</t>
+          <t>[124.4, 280.2, 175.8]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>115.5482412933042</v>
+        <v>68.0978603931613</v>
       </c>
       <c r="G160" t="n">
-        <v>105.8210182823922</v>
+        <v>60.57756305614154</v>
       </c>
       <c r="H160" t="n">
-        <v>55.16352831825388</v>
+        <v>30.11344150050073</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[361.53, 281.23, 347.87]</t>
+          <t>[200.17, 90.74, 63.09]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[261.9, 145.4, 401.1]</t>
+          <t>[280.2, 175.8, 26.8]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>101.9979934470231</v>
+        <v>70.60895928488966</v>
       </c>
       <c r="G161" t="n">
-        <v>96.23281767652406</v>
+        <v>67.1259285078276</v>
       </c>
       <c r="H161" t="n">
-        <v>48.24456222618643</v>
+        <v>70.78219149983336</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[242.35, 300.22, 288.26]</t>
+          <t>[0.44, 3.17, 1.57]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[145.4, 401.1, 146.9]</t>
+          <t>[3.1, 8.7, 6.0]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>114.832989610698</v>
+        <v>4.369651492111524</v>
       </c>
       <c r="G162" t="n">
-        <v>113.0648744608839</v>
+        <v>4.207316872546034</v>
       </c>
       <c r="H162" t="n">
-        <v>62.68689549346195</v>
+        <v>74.43496022895366</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[236.99, 228.03, 219.28]</t>
+          <t>[5.36, 2.86, 2.02]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[401.1, 146.9, 128.7]</t>
+          <t>[8.7, 6.0, 2.0]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>117.9219340363519</v>
+        <v>2.648499101781298</v>
       </c>
       <c r="G163" t="n">
-        <v>111.9366020784123</v>
+        <v>2.16727569203226</v>
       </c>
       <c r="H163" t="n">
-        <v>55.50581052064841</v>
+        <v>30.55247677194352</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[290.8, 279.05, 342.95]</t>
+          <t>[3.74, 2.68, 11.22]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[146.9, 128.7, 374.48]</t>
+          <t>[6.0, 2.0, 12.6]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>121.5291715048414</v>
+        <v>1.578869977049308</v>
       </c>
       <c r="G164" t="n">
-        <v>108.5940840671429</v>
+        <v>1.440862366725649</v>
       </c>
       <c r="H164" t="n">
-        <v>74.40102009444158</v>
+        <v>27.59037615843099</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[204.07, 251.56, 398.76]</t>
+          <t>[3.45, 13.68, 0.36]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>[128.7, 374.48, 385.73]</t>
+          <t>[2.0, 12.6, 0.0]</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>83.58755194560027</v>
+        <v>1.065276970207742</v>
       </c>
       <c r="G165" t="n">
-        <v>70.44010123540356</v>
-      </c>
-      <c r="H165" t="n">
-        <v>31.58803789622808</v>
+        <v>0.9647700760429351</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[203.33, 323.03, 369.09]</t>
+          <t>[11.28, 0.14, 1.17]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[374.48, 385.73, 449.35]</t>
+          <t>[12.6, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>114.9851029187112</v>
+        <v>1.022107815987613</v>
       </c>
       <c r="G166" t="n">
-        <v>104.7028971299727</v>
-      </c>
-      <c r="H166" t="n">
-        <v>26.60645133024686</v>
+        <v>0.8782982324615878</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[252.49, 225.05, 303.5]</t>
+          <t>[0.2, 1.26, 3.14]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[277.85, 312.87, 200.81]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>79.37219755604546</v>
+        <v>1.956439223317449</v>
       </c>
       <c r="G167" t="n">
-        <v>71.95568857058309</v>
-      </c>
-      <c r="H167" t="n">
-        <v>29.4442614831389</v>
+        <v>1.531598932132628</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[230.82, 311.19, 247.93]</t>
+          <t>[1.09, 2.85, 0.51]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[312.87, 200.81, 156.16]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>95.46009407805288</v>
+        <v>1.78595882862709</v>
       </c>
       <c r="G168" t="n">
-        <v>94.73408006897994</v>
-      </c>
-      <c r="H168" t="n">
-        <v>46.65322236719093</v>
+        <v>1.484786863754231</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[337.12, 268.38, 215.5]</t>
+          <t>[1.82, 0.12, 0.14]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>[200.81, 156.16, 28.9]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>148.3148957471809</v>
+        <v>1.055850100526618</v>
       </c>
       <c r="G169" t="n">
-        <v>145.0424337538515</v>
-      </c>
-      <c r="H169" t="n">
-        <v>261.8008186206764</v>
+        <v>0.6918301064188869</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[234.56, 188.52, 251.66]</t>
+          <t>[-0.31, -0.29, 2.12]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>[156.16, 28.9, 141.33]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>120.8247631697429</v>
+        <v>1.249619470094538</v>
       </c>
       <c r="G170" t="n">
-        <v>116.1138982670695</v>
-      </c>
-      <c r="H170" t="n">
-        <v>226.8585228206023</v>
+        <v>0.9065563244625801</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[169.42, 226.38, 269.54]</t>
+          <t>[-0.15, 2.72, 2.83]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>[28.9, 141.33, 214.21]</t>
+          <t>[0.0, 0.0, 9.5]</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>100.0706656081673</v>
+        <v>4.162193002232242</v>
       </c>
       <c r="G171" t="n">
-        <v>93.63576471406435</v>
-      </c>
-      <c r="H171" t="n">
-        <v>190.7513108487305</v>
+        <v>3.181790607071605</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[131.92, 157.89, 154.33]</t>
+          <t>[290.8, 279.05, 342.95]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[141.33, 214.21, 397.76]</t>
+          <t>[146.9, 128.7, 374.48]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>144.3609659075435</v>
+        <v>121.5291715048414</v>
       </c>
       <c r="G172" t="n">
-        <v>103.0534768524319</v>
+        <v>108.5940840671429</v>
       </c>
       <c r="H172" t="n">
-        <v>31.38306354991335</v>
+        <v>74.40102009444158</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[162.31, 158.62, 130.7]</t>
+          <t>[204.07, 251.56, 398.76]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>[214.21, 397.76, 482.39]</t>
+          <t>[128.7, 374.48, 385.73]</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>247.3652508251625</v>
+        <v>83.58755194560027</v>
       </c>
       <c r="G173" t="n">
-        <v>214.2427654711719</v>
+        <v>70.44010123540356</v>
       </c>
       <c r="H173" t="n">
-        <v>52.41821727621955</v>
+        <v>31.58803789622808</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[173.78, 143.1, 482.27]</t>
+          <t>[203.33, 323.03, 369.09]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>[397.76, 482.39, 731.53]</t>
+          <t>[374.48, 385.73, 449.35]</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>275.3280313349862</v>
+        <v>114.9851029187112</v>
       </c>
       <c r="G174" t="n">
-        <v>270.8441811355199</v>
+        <v>104.7028971299727</v>
       </c>
       <c r="H174" t="n">
-        <v>53.57342666980857</v>
+        <v>26.60645133024686</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[180.17, 605.4, 247.15]</t>
+          <t>[427.52, 487.25, 182.7]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>[482.39, 731.53, 509.18]</t>
+          <t>[385.73, 449.35, 319.17]</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>242.1484470048273</v>
+        <v>85.26072920662314</v>
       </c>
       <c r="G175" t="n">
-        <v>230.1283472670095</v>
+        <v>72.05583026689045</v>
       </c>
       <c r="H175" t="n">
-        <v>43.78484225598421</v>
+        <v>20.67608404601183</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[784.53, 319.72, 464.16]</t>
+          <t>[464.91, 174.37, 140.65]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>[731.53, 509.18, 363.28]</t>
+          <t>[449.35, 319.17, 252.85]</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>127.6475142789027</v>
+        <v>106.141725038271</v>
       </c>
       <c r="G176" t="n">
-        <v>114.4474200660934</v>
+        <v>90.8528053005296</v>
       </c>
       <c r="H176" t="n">
-        <v>24.07440653636285</v>
+        <v>31.06815108510734</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[338.46, 672.8, 554.71]</t>
+          <t>[171.69, 138.5, 192.43]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[891.03, 302.31, 918.78]</t>
+          <t>[319.17, 252.85, 234.53]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>437.8542263799057</v>
+        <v>110.4537478276725</v>
       </c>
       <c r="G177" t="n">
-        <v>429.0454262544587</v>
+        <v>101.310938346032</v>
       </c>
       <c r="H177" t="n">
-        <v>74.73157585244662</v>
+        <v>36.46107965244602</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[1235.28, 1009.02, 1678.16]</t>
+          <t>[184.25, 255.25, 287.5]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[302.31, 918.78, 612.13]</t>
+          <t>[252.85, 234.53, 559.95]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>819.5525685071171</v>
+        <v>162.6469118279242</v>
       </c>
       <c r="G178" t="n">
-        <v>696.4153146611552</v>
+        <v>120.5869310515197</v>
       </c>
       <c r="H178" t="n">
-        <v>164.1958108700239</v>
+        <v>28.20616596041596</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[465.92, 785.03, 615.63]</t>
+          <t>[295.32, 332.22, 353.03]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[918.78, 612.13, 333.1]</t>
+          <t>[234.53, 559.95, 564.43]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>323.9341851956767</v>
+        <v>182.7973662933436</v>
       </c>
       <c r="G179" t="n">
-        <v>302.7642276609511</v>
+        <v>166.6383203343865</v>
       </c>
       <c r="H179" t="n">
-        <v>54.11805497503514</v>
+        <v>34.68069124581398</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[1098.48, 856.97, 1046.61]</t>
+          <t>[298.84, 317.84, 239.21]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[612.13, 333.1, 305.92]</t>
+          <t>[559.95, 564.43, 819.96]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>594.3018428480678</v>
+        <v>394.2301256281076</v>
       </c>
       <c r="G180" t="n">
-        <v>583.6327383009757</v>
+        <v>362.8146269404087</v>
       </c>
       <c r="H180" t="n">
-        <v>159.6129589848794</v>
+        <v>53.71494490575013</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[650.48, 798.62, 339.93]</t>
+          <t>[423.87, 318.36, 425.91]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[333.1, 305.92, 742.4]</t>
+          <t>[564.43, 819.96, 914.28]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>410.4748888361123</v>
+        <v>412.2532654829869</v>
       </c>
       <c r="G181" t="n">
-        <v>404.1850336408558</v>
+        <v>376.8405605975997</v>
       </c>
       <c r="H181" t="n">
-        <v>103.5162183053404</v>
+        <v>46.49714184985772</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[576.51, 246.32, 488.39]</t>
+          <t>[173.78, 143.1, 482.27]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[305.92, 742.4, 700.6]</t>
+          <t>[397.76, 482.39, 731.53]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>348.494248345648</v>
+        <v>275.3280313349862</v>
       </c>
       <c r="G182" t="n">
-        <v>326.2917261526267</v>
+        <v>270.8441811355199</v>
       </c>
       <c r="H182" t="n">
-        <v>61.85386804819504</v>
+        <v>53.57342666980857</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[174.65, 348.34, 252.94]</t>
+          <t>[180.17, 605.4, 247.15]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[742.4, 700.6, 711.12]</t>
+          <t>[482.39, 731.53, 509.18]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>467.7444954573166</v>
+        <v>242.1484470048273</v>
       </c>
       <c r="G183" t="n">
-        <v>459.3960125538593</v>
+        <v>230.1283472670095</v>
       </c>
       <c r="H183" t="n">
-        <v>63.72839476969047</v>
+        <v>43.78484225598421</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[688.79, 495.89, 635.55]</t>
+          <t>[784.53, 319.72, 464.16]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[700.6, 711.12, 691.74]</t>
+          <t>[731.53, 509.18, 363.28]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>128.6063012413043</v>
+        <v>127.6475142789027</v>
       </c>
       <c r="G184" t="n">
-        <v>94.40941255539934</v>
+        <v>114.4474200660934</v>
       </c>
       <c r="H184" t="n">
-        <v>13.35826292007984</v>
+        <v>24.07440653636285</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[499.73, 640.42, 517.96]</t>
+          <t>[313.3, 454.94, 238.28]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[711.12, 691.74, 667.3]</t>
+          <t>[509.18, 363.28, 414.05]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>152.3366566304178</v>
+        <v>160.8967296834721</v>
       </c>
       <c r="G185" t="n">
-        <v>137.3486330464021</v>
+        <v>154.4338870653423</v>
       </c>
       <c r="H185" t="n">
-        <v>19.841485287957</v>
+        <v>35.3834257205428</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[522.54, 273.56, 249.5]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[363.28, 414.05, 496.82]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>188.2118320734676</v>
+      </c>
+      <c r="G186" t="n">
+        <v>182.358885909854</v>
+      </c>
+      <c r="H186" t="n">
+        <v>42.51744437865156</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[246.45, 224.95, 281.79]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[414.05, 496.82, 705.66]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>306.4156394354155</v>
+      </c>
+      <c r="G187" t="n">
+        <v>287.7815241017059</v>
+      </c>
+      <c r="H187" t="n">
+        <v>51.75608759868554</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[259.35, 324.46, 257.73]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[496.82, 705.66, 574.51]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>317.3116080291211</v>
+      </c>
+      <c r="G188" t="n">
+        <v>311.8190824550043</v>
+      </c>
+      <c r="H188" t="n">
+        <v>52.31955181823048</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[394.57, 312.9, 217.05]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[705.66, 574.51, 682.01]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>356.5590981632121</v>
+      </c>
+      <c r="G189" t="n">
+        <v>345.8861547718103</v>
+      </c>
+      <c r="H189" t="n">
+        <v>52.5986281928194</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[380.78, 263.78, 398.05]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[574.51, 682.01, 730.13]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>327.9882882562976</v>
+      </c>
+      <c r="G190" t="n">
+        <v>314.6817625109164</v>
+      </c>
+      <c r="H190" t="n">
+        <v>46.84236540213173</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[305.98, 461.05, 558.41]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[682.01, 730.13, 978.55]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>360.7034544673843</v>
+      </c>
+      <c r="G191" t="n">
+        <v>355.0835564019569</v>
+      </c>
+      <c r="H191" t="n">
+        <v>44.97479277476524</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[688.79, 495.89, 635.55]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[700.6, 711.12, 691.74]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>128.6063012413043</v>
+      </c>
+      <c r="G192" t="n">
+        <v>94.40941255539934</v>
+      </c>
+      <c r="H192" t="n">
+        <v>13.35826292007984</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[499.73, 640.42, 517.96]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[711.12, 691.74, 667.3]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>152.3366566304178</v>
+      </c>
+      <c r="G193" t="n">
+        <v>137.3486330464021</v>
+      </c>
+      <c r="H193" t="n">
+        <v>19.841485287957</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[750.39, 605.74, 915.06]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[691.74, 667.3, 565.34]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>207.793780424108</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>156.6455901452823</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>26.52166197359558</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[583.86, 882.5, 417.97]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[667.3, 565.34, 810.6]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>295.3606311633279</v>
+      </c>
+      <c r="G195" t="n">
+        <v>264.4102918018171</v>
+      </c>
+      <c r="H195" t="n">
+        <v>39.01396122256276</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[936.65, 443.47, 656.27]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[565.34, 810.6, 641.64]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>301.5922432598692</v>
+      </c>
+      <c r="G196" t="n">
+        <v>251.0255030753528</v>
+      </c>
+      <c r="H196" t="n">
+        <v>37.75043668047343</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[354.92, 526.86, 541.42]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[810.6, 641.64, 802.3]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>310.3101321187725</v>
+      </c>
+      <c r="G197" t="n">
+        <v>277.112840393445</v>
+      </c>
+      <c r="H197" t="n">
+        <v>35.53997364793467</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[751.03, 767.97, 1103.05]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[641.64, 802.3, 750.07]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>214.2721576091303</v>
+      </c>
+      <c r="G198" t="n">
+        <v>165.565824175591</v>
+      </c>
+      <c r="H198" t="n">
+        <v>22.7956175486736</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[717.59, 1031.78, 758.58]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[802.3, 750.07, 754.31]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>169.8567959419353</v>
+      </c>
+      <c r="G199" t="n">
+        <v>123.564771837355</v>
+      </c>
+      <c r="H199" t="n">
+        <v>16.22761859830753</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[1081.73, 794.83, 942.02]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[750.07, 754.31, 925.67]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>193.1414420236267</v>
+      </c>
+      <c r="G200" t="n">
+        <v>129.5123740271649</v>
+      </c>
+      <c r="H200" t="n">
+        <v>17.11871907349467</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[681.34, 809.57, 441.28]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[754.31, 925.67, 627.6]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>133.5634034386553</v>
+      </c>
+      <c r="G201" t="n">
+        <v>125.1286675866153</v>
+      </c>
+      <c r="H201" t="n">
+        <v>17.30098968737461</v>
       </c>
     </row>
   </sheetData>
